--- a/docs/curated_assembly_stats_v2.xlsx
+++ b/docs/curated_assembly_stats_v2.xlsx
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2222138</v>
+        <v>2228424</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>444427.6</v>
+        <v>445684.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2042160</v>
+        <v>2048446</v>
       </c>
       <c r="G11" t="n">
         <v>12032</v>
       </c>
       <c r="H11" t="n">
-        <v>2042160</v>
+        <v>2048446</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
